--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487792_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487792_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8028</v>
+        <v>2.57</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6457</v>
+        <v>3.4128</v>
       </c>
       <c r="F2" t="n">
         <v>-0.8428</v>
@@ -610,10 +610,10 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5343</v>
+        <v>-0.7672</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4873</v>
+        <v>0.2544</v>
       </c>
       <c r="U2" t="n">
         <v>-1.0216</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0665</v>
+        <v>0.4406</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6441</v>
+        <v>1.0181</v>
       </c>
       <c r="F3" t="n">
         <v>-0.5776</v>
@@ -688,10 +688,10 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2984</v>
+        <v>0.6725</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8914</v>
+        <v>1.2654</v>
       </c>
       <c r="U3" t="n">
         <v>-0.593</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1736</v>
+        <v>0.2799</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8282</v>
+        <v>-0.6977</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="G4" t="n">
         <v>1.5096</v>
@@ -766,13 +766,13 @@
         <v>0.2081</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5801</v>
+        <v>-1.1267</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6524</v>
+        <v>-0.5219</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9277</v>
+        <v>-0.6047</v>
       </c>
       <c r="V4" t="n">
         <v>0.9376</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.625</v>
+        <v>-1.1414</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.6304</v>
+        <v>-2.0294</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0054</v>
+        <v>0.888</v>
       </c>
       <c r="G5" t="n">
         <v>-3.134</v>
@@ -844,13 +844,13 @@
         <v>2.7055</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.5048</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0315</v>
+        <v>-0.4305</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0431</v>
+        <v>-0.0743</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Í. IBAÑEZ SERRANO</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8061</v>
+        <v>-1.435</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9959</v>
+        <v>1.3026</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8102</v>
+        <v>-2.7376</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.519</v>
+        <v>-0.6506</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5671</v>
+        <v>1.1578</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9519</v>
+        <v>-1.8084</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5392</v>
+        <v>2.3459</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0576</v>
+        <v>1.9868</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5968</v>
+        <v>0.3592</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9798</v>
+        <v>-2.9966</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6247</v>
+        <v>-0.829</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3551</v>
+        <v>-2.1676</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4162</v>
+        <v>3.1218</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3373</v>
+        <v>-0.7844</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5839</v>
+        <v>-0.2566</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2466</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>Í. IBAÑEZ SERRANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6157</v>
+        <v>-1.8965</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3568</v>
+        <v>-1.145</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9724</v>
+        <v>-0.7514</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6506</v>
+        <v>-1.519</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1578</v>
+        <v>-0.5671</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8084</v>
+        <v>-0.9519</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3459</v>
+        <v>-0.5392</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9868</v>
+        <v>0.0576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3592</v>
+        <v>-0.5968</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9966</v>
+        <v>-0.9798</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.829</v>
+        <v>-0.6247</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1676</v>
+        <v>-0.3551</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1218</v>
+        <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9651</v>
+        <v>0.2469</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2025</v>
+        <v>0.4348</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-0.1879</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4225</v>
+        <v>-2.76</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1462</v>
+        <v>-1.3075</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2764</v>
+        <v>-1.4525</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1847</v>
@@ -1078,13 +1078,13 @@
         <v>2.0812</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4033</v>
+        <v>-0.7408</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0191</v>
+        <v>-0.1804</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3842</v>
+        <v>-0.5604</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8751</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.0341</v>
+        <v>-4.5565</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.3283</v>
+        <v>-5.7039</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2942</v>
+        <v>1.1474</v>
       </c>
       <c r="G9" t="n">
         <v>-3.759</v>
@@ -1156,13 +1156,13 @@
         <v>2.0812</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8776</v>
+        <v>-1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4106</v>
+        <v>-0.7862</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.467</v>
+        <v>-0.6138</v>
       </c>
       <c r="V9" t="n">
         <v>-0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.5509</v>
+        <v>-7.5547</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.1743</v>
+        <v>-5.0019</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3766</v>
+        <v>-2.5528</v>
       </c>
       <c r="G10" t="n">
         <v>-4.366</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1828</v>
+        <v>-1.1866</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.901</v>
+        <v>-0.7286</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2818</v>
+        <v>-0.4579</v>
       </c>
       <c r="V10" t="n">
         <v>-3.0427</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-17.3586</v>
+        <v>-16.0536</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.4567</v>
+        <v>-10.1519</v>
       </c>
       <c r="F11" t="n">
         <v>-5.9017</v>
@@ -1312,13 +1312,13 @@
         <v>15.6088</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.8959</v>
+        <v>-5.591100000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.2545</v>
+        <v>-0.9496</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.6414</v>
+        <v>-4.641299999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7252999999999998</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9782</v>
+        <v>7.2259</v>
       </c>
       <c r="E12" t="n">
-        <v>4.3324</v>
+        <v>4.9753</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6458</v>
+        <v>2.2506</v>
       </c>
       <c r="G12" t="n">
         <v>4.5031</v>
@@ -1390,13 +1390,13 @@
         <v>2.2893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2336</v>
+        <v>1.0142</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3047</v>
+        <v>0.3382</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0712</v>
+        <v>0.676</v>
       </c>
       <c r="V12" t="n">
         <v>0.4599</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3952</v>
+        <v>4.8825</v>
       </c>
       <c r="E13" t="n">
         <v>2.3989</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9963</v>
+        <v>2.4837</v>
       </c>
       <c r="G13" t="n">
         <v>2.4611</v>
@@ -1468,13 +1468,13 @@
         <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6635</v>
+        <v>1.1508</v>
       </c>
       <c r="T13" t="n">
         <v>0.6706</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0071</v>
+        <v>0.4802</v>
       </c>
       <c r="V13" t="n">
         <v>0.23</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2293</v>
+        <v>3.2038</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5822</v>
+        <v>3.2963</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3529</v>
+        <v>-0.0926</v>
       </c>
       <c r="G14" t="n">
         <v>2.744</v>
@@ -1546,13 +1546,13 @@
         <v>0.6244</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7153</v>
+        <v>1.6897</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3479</v>
+        <v>1.0621</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3673</v>
+        <v>0.6277</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8137</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. PA MOR</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9634</v>
+        <v>2.3333</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9371</v>
+        <v>0.8106</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0263</v>
+        <v>1.5227</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4132</v>
+        <v>1.6451</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2131</v>
+        <v>1.3178</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.3274</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0336</v>
+        <v>0.7227</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1623</v>
+        <v>1.6118</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1959</v>
+        <v>-0.8891</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3796</v>
+        <v>0.9224</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3755</v>
+        <v>-0.294</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0041</v>
+        <v>1.2165</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0102</v>
+        <v>-0.0194</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3603</v>
+        <v>-0.039</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6499</v>
+        <v>0.0196</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1238</v>
+        <v>0.7076</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5838</v>
+        <v>1.1675</v>
       </c>
       <c r="X15" t="n">
         <v>-0.4599</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>D. PA MOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5802</v>
+        <v>2.3316</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2062</v>
+        <v>0.5441</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7864</v>
+        <v>1.7875</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0948</v>
+        <v>0.4132</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3454</v>
+        <v>0.2131</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4402</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1747</v>
+        <v>0.0336</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2922</v>
+        <v>-0.1623</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1176</v>
+        <v>0.1959</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2695</v>
+        <v>0.3796</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0532</v>
+        <v>0.3755</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3226</v>
+        <v>0.0041</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1941</v>
+        <v>1.3784</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0497</v>
+        <v>0.9673</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1444</v>
+        <v>0.4111</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4599</v>
+        <v>0.1238</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X16" t="n">
         <v>-0.4599</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4492</v>
+        <v>0.9577</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2748</v>
+        <v>-0.2525</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1743</v>
+        <v>1.2102</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6451</v>
+        <v>2.7885</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3178</v>
+        <v>-2.1239</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3274</v>
+        <v>4.9124</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7227</v>
+        <v>2.9152</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6118</v>
+        <v>-1.6339</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8891</v>
+        <v>4.5491</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9224</v>
+        <v>-0.1267</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.294</v>
+        <v>-0.4901</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2165</v>
+        <v>0.3633</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-3.3299</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-5.2029</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9036</v>
+        <v>0.3316</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5748</v>
+        <v>0.2839</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3288</v>
+        <v>0.0477</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7076</v>
+        <v>1.1675</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>1.7513</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4599</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.498</v>
+        <v>0.7367</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.217</v>
+        <v>-1.6348</v>
       </c>
       <c r="F18" t="n">
-        <v>0.719</v>
+        <v>2.3714</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7885</v>
+        <v>1.0948</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1239</v>
+        <v>-0.3454</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9124</v>
+        <v>1.4402</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9152</v>
+        <v>-0.1747</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6339</v>
+        <v>-0.2922</v>
       </c>
       <c r="L18" t="n">
-        <v>4.5491</v>
+        <v>0.1176</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1267</v>
+        <v>1.2695</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4901</v>
+        <v>-0.0532</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3633</v>
+        <v>1.3226</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.2029</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1241</v>
+        <v>1.3505</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6805</v>
+        <v>0.6211</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4436</v>
+        <v>0.7294</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1675</v>
+        <v>-0.4599</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5838</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1968</v>
+        <v>-0.5793</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3007</v>
+        <v>-2.0864</v>
       </c>
       <c r="F19" t="n">
-        <v>1.104</v>
+        <v>1.5071</v>
       </c>
       <c r="G19" t="n">
         <v>-1.763</v>
@@ -1936,13 +1936,13 @@
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9232</v>
+        <v>1.5407</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2296</v>
+        <v>0.4439</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6936</v>
+        <v>1.0967</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3975</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5424</v>
+        <v>-1.5907</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8999</v>
+        <v>-2.1498</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3575</v>
+        <v>0.5591</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0279</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.349</v>
+        <v>0.6027</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4567</v>
+        <v>0.2934</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1077</v>
+        <v>0.3093</v>
       </c>
       <c r="V20" t="n">
         <v>0.7076</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>17.3583</v>
+        <v>19.5015</v>
       </c>
       <c r="E21" t="n">
-        <v>5.901599999999998</v>
+        <v>5.901700000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>11.4567</v>
+        <v>13.5997</v>
       </c>
       <c r="G21" t="n">
         <v>12.8589</v>
@@ -2092,22 +2092,22 @@
         <v>12.4872</v>
       </c>
       <c r="S21" t="n">
-        <v>6.896</v>
+        <v>9.039200000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>4.6414</v>
+        <v>4.641500000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2546</v>
+        <v>4.3977</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7253000000000001</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>7.1114</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.3859</v>
+        <v>-6.385899999999999</v>
       </c>
     </row>
   </sheetData>
